--- a/AtchisonRegime/Outputs/China/China_Eq/df_regSummary_China_Eq.xlsx
+++ b/AtchisonRegime/Outputs/China/China_Eq/df_regSummary_China_Eq.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>1.327193407704851</v>
+        <v>1.344776664734815</v>
       </c>
       <c r="H2" t="n">
-        <v>5.108640939288379</v>
+        <v>5.001851258233686</v>
       </c>
       <c r="I2" t="n">
         <v>-6.49330771413728</v>
@@ -545,22 +545,22 @@
         <v>12.1040808797468</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>24.75247524752475</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06413643788220764</v>
+        <v>0.06832888335471712</v>
       </c>
       <c r="O2" t="n">
         <v>-0.06711984032740836</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1864685281693315</v>
+        <v>0.2074307555318788</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>23.8494781687939</v>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>22.77227722772277</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>21.1810668982901</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>29.7029702970297</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -719,7 +719,7 @@
         <v>8.65395055376516</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>22.77227722772277</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
